--- a/data/overrides_template.xlsx
+++ b/data/overrides_template.xlsx
@@ -619,7 +619,11 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -644,7 +648,11 @@
       <c r="D8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -669,7 +677,11 @@
       <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PTBKCAHM0000</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
